--- a/test-files/дубли.xlsx
+++ b/test-files/дубли.xlsx
@@ -423,7 +423,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E9"/>
+  <dimension ref="A1:E26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -531,28 +531,32 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Лебедева Светлана Петровна</t>
+          <t>Кузнецов Дмитрий Сергеевич</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Тестировщик</t>
+          <t>Дизайнер</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Аналитика</t>
+          <t>Дизайн</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>167212</v>
-      </c>
-      <c r="E5" t="inlineStr"/>
+        <v>110000</v>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>04.02.2021</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Волков Антон Игоревич</t>
+          <t>Смирнов Владимир Андреевич</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -562,43 +566,47 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Аналитика</t>
+          <t>Финансы</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>298487</v>
-      </c>
-      <c r="E6" t="inlineStr"/>
+        <v>85000</v>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>20.11.2019</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Новикова Дарья Викторовна</t>
+          <t>Соколов Михаил Викторович</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Финансовый аналитик</t>
+          <t>Тестировщик</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Аналитика</t>
+          <t>Разработка</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>228103</v>
+        <v>90000</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>08.05.2018</t>
+          <t>07.07.2022</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Смирнов Владимир Андреевич</t>
+          <t>Попов Андрей Дмитриевич</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -608,32 +616,449 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Дизайн</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr"/>
-      <c r="E8" t="inlineStr"/>
+          <t>HR</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>78000</v>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>15.01.2020</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
+          <t>Лебедев Сергей Александрович</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Старший разработчик</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Разработка</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>220000</v>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>03.05.2017</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Иванова Анна Сергеевна</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>UX-исследователь</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Дизайн</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>130000</v>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>11.08.2021</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
           <t>Козлова Юлия Романовна</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Финансовый аналитик</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Финансы</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>140000</v>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>22.04.2018</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Иванов Иван Иванович</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Менеджер</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Продажи</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
+        <v>75000</v>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>15.03.2020</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Петрова Мария Викторовна</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Аналитик</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Аналитика</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
+        <v>95000</v>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>01.06.2019</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Сидоров Алексей Николаевич</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Тимлид</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Разработка</t>
+        </is>
+      </c>
+      <c r="D14" t="n">
+        <v>180000</v>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>12.09.2018</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Кузнецов Дмитрий Сергеевич</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Дизайнер</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Дизайн</t>
+        </is>
+      </c>
+      <c r="D15" t="n">
+        <v>110000</v>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>04.02.2021</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Смирнов Владимир Андреевич</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Бухгалтер</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Финансы</t>
+        </is>
+      </c>
+      <c r="D16" t="n">
+        <v>85000</v>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>20.11.2019</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Соколов Михаил Викторович</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Тестировщик</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Разработка</t>
+        </is>
+      </c>
+      <c r="D17" t="n">
+        <v>90000</v>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>07.07.2022</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Попов Андрей Дмитриевич</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>HR-специалист</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>HR</t>
+        </is>
+      </c>
+      <c r="D18" t="n">
+        <v>78000</v>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>15.01.2020</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Лебедев Сергей Александрович</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
         <is>
           <t>Старший разработчик</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr">
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Разработка</t>
+        </is>
+      </c>
+      <c r="D19" t="n">
+        <v>220000</v>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>03.05.2017</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Иванова Анна Сергеевна</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>UX-исследователь</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Дизайн</t>
+        </is>
+      </c>
+      <c r="D20" t="n">
+        <v>130000</v>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>11.08.2021</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Козлова Юлия Романовна</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Финансовый аналитик</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Финансы</t>
+        </is>
+      </c>
+      <c r="D21" t="n">
+        <v>140000</v>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>22.04.2018</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Лебедева Светлана Петровна</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Тестировщик</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Аналитика</t>
+        </is>
+      </c>
+      <c r="D22" t="n">
+        <v>167212</v>
+      </c>
+      <c r="E22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Волков Антон Игоревич</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Бухгалтер</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Аналитика</t>
+        </is>
+      </c>
+      <c r="D23" t="n">
+        <v>298487</v>
+      </c>
+      <c r="E23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Новикова Дарья Викторовна</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Финансовый аналитик</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Аналитика</t>
+        </is>
+      </c>
+      <c r="D24" t="n">
+        <v>228103</v>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>08.05.2018</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Смирнов Владимир Андреевич</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>HR-специалист</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Дизайн</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr"/>
+      <c r="E25" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>Козлова Юлия Романовна</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Старший разработчик</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
         <is>
           <t>Поддержка</t>
         </is>
       </c>
-      <c r="D9" t="n">
+      <c r="D26" t="n">
         <v>208621</v>
       </c>
-      <c r="E9" t="inlineStr">
+      <c r="E26" t="inlineStr">
         <is>
           <t>17.01.2023</t>
         </is>
